--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N110_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N110_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.69071548096427</v>
+        <v>3.849741265656694</v>
       </c>
       <c r="D2" t="n">
-        <v>31.87464158327845</v>
+        <v>5.179629257282748</v>
       </c>
       <c r="E2" t="n">
-        <v>33.35868121739697</v>
+        <v>5.420785697827009</v>
       </c>
       <c r="F2" t="n">
-        <v>30.17151007188686</v>
+        <v>4.902870386681614</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>10.5625</v>
       </c>
       <c r="D3" t="n">
-        <v>77.91851473348042</v>
+        <v>12.66175864419057</v>
       </c>
       <c r="E3" t="n">
-        <v>33.35868121739697</v>
+        <v>5.420785697827009</v>
       </c>
       <c r="F3" t="n">
-        <v>30.17151007188686</v>
+        <v>4.902870386681614</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.95503655162647</v>
+        <v>9.580193439639302</v>
       </c>
       <c r="D4" t="n">
-        <v>74.47010246497904</v>
+        <v>12.10139165055909</v>
       </c>
       <c r="E4" t="n">
-        <v>33.35868121739697</v>
+        <v>5.420785697827009</v>
       </c>
       <c r="F4" t="n">
-        <v>30.17151007188686</v>
+        <v>4.902870386681614</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>117.0943865314725</v>
+        <v>19.02783781136429</v>
       </c>
       <c r="D5" t="n">
-        <v>117.108855317251</v>
+        <v>19.03018898905329</v>
       </c>
       <c r="E5" t="n">
-        <v>33.35868121739697</v>
+        <v>5.420785697827009</v>
       </c>
       <c r="F5" t="n">
-        <v>30.17151007188686</v>
+        <v>4.902870386681614</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
